--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487024_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487024_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.636</v>
+        <v>7.63</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9373</v>
+        <v>6.7238</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6988</v>
+        <v>0.9063</v>
       </c>
       <c r="G2" t="n">
         <v>3.8928</v>
@@ -610,13 +610,13 @@
         <v>2.2588</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0433</v>
+        <v>-0.0493</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8486</v>
+        <v>-0.0621</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1947</v>
+        <v>0.0128</v>
       </c>
       <c r="V2" t="n">
         <v>1.5277</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8889</v>
+        <v>6.0008</v>
       </c>
       <c r="E3" t="n">
-        <v>5.762</v>
+        <v>5.6071</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1269</v>
+        <v>0.3937</v>
       </c>
       <c r="G3" t="n">
         <v>2.9401</v>
@@ -688,13 +688,13 @@
         <v>2.8748</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1274</v>
+        <v>0.2393</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2903</v>
+        <v>0.1354</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1629</v>
+        <v>0.1039</v>
       </c>
       <c r="V3" t="n">
         <v>1.1786</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5075</v>
+        <v>2.8965</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7009</v>
+        <v>1.6234</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8066</v>
+        <v>1.2731</v>
       </c>
       <c r="G4" t="n">
         <v>-1.1567</v>
@@ -766,13 +766,13 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6436</v>
+        <v>1.0326</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3176</v>
+        <v>0.2401</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3261</v>
+        <v>0.7925</v>
       </c>
       <c r="V4" t="n">
         <v>2.8152</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.592</v>
+        <v>1.9765</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2071</v>
+        <v>0.4434</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3849</v>
+        <v>1.5331</v>
       </c>
       <c r="G5" t="n">
         <v>3.3567</v>
@@ -844,13 +844,13 @@
         <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9434</v>
+        <v>-0.5588</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3875</v>
+        <v>-0.1512</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.4076</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4525</v>
+        <v>0.1692</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8226</v>
+        <v>-0.6909</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2751</v>
+        <v>0.8601</v>
       </c>
       <c r="G6" t="n">
         <v>1.194</v>
@@ -922,13 +922,13 @@
         <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4247</v>
+        <v>0.1415</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2635</v>
+        <v>-0.1317</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6882</v>
+        <v>0.2732</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9609</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1775</v>
+        <v>-0.9816</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1331</v>
+        <v>-1.1447</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0444</v>
+        <v>0.1631</v>
       </c>
       <c r="G7" t="n">
         <v>0.819</v>
@@ -1000,13 +1000,13 @@
         <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3886</v>
+        <v>-0.1927</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0272</v>
+        <v>-0.0388</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3614</v>
+        <v>-0.1539</v>
       </c>
       <c r="V7" t="n">
         <v>0.2402</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5456</v>
+        <v>-2.0704</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.125</v>
+        <v>-0.6795</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4205</v>
+        <v>-1.3909</v>
       </c>
       <c r="G8" t="n">
         <v>1.8728</v>
@@ -1078,13 +1078,13 @@
         <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5467</v>
+        <v>1.0219</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5115</v>
+        <v>-0.066</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0583</v>
+        <v>1.0879</v>
       </c>
       <c r="V8" t="n">
         <v>-2.7063</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7785</v>
+        <v>-3.1789</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1461</v>
+        <v>-3.5761</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3676</v>
+        <v>0.3972</v>
       </c>
       <c r="G9" t="n">
         <v>-4.0884</v>
@@ -1156,13 +1156,13 @@
         <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0697</v>
+        <v>0.6693</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4066</v>
+        <v>-0.0234</v>
       </c>
       <c r="U9" t="n">
-        <v>0.663</v>
+        <v>0.6927</v>
       </c>
       <c r="V9" t="n">
         <v>0.2402</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.57</v>
+        <v>-4.79</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1082</v>
+        <v>-3.3876</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4618</v>
+        <v>-1.4025</v>
       </c>
       <c r="G10" t="n">
         <v>-5.937</v>
@@ -1234,13 +1234,13 @@
         <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5261</v>
+        <v>0.2538</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9726</v>
+        <v>-0.252</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4465</v>
+        <v>0.5058</v>
       </c>
       <c r="V10" t="n">
         <v>2.9466</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.005299999999998</v>
+        <v>7.652100000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>3.272299999999998</v>
+        <v>4.918900000000002</v>
       </c>
       <c r="F11" t="n">
         <v>2.733199999999999</v>
@@ -1312,13 +1312,13 @@
         <v>16.4275</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9107000000000001</v>
+        <v>2.5576</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.9964</v>
+        <v>-0.3497</v>
       </c>
       <c r="U11" t="n">
-        <v>2.9072</v>
+        <v>2.9073</v>
       </c>
       <c r="V11" t="n">
         <v>5.2813</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4187</v>
+        <v>5.2843</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2408</v>
+        <v>3.45</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1779</v>
+        <v>1.8343</v>
       </c>
       <c r="G12" t="n">
         <v>0.9393</v>
@@ -1390,13 +1390,13 @@
         <v>3.0801</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4259</v>
+        <v>0.2915</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5465</v>
+        <v>-0.3373</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9724</v>
+        <v>0.6288</v>
       </c>
       <c r="V12" t="n">
         <v>1.1786</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.316</v>
+        <v>0.8522</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0372</v>
+        <v>-0.4858</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2787</v>
+        <v>1.338</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7618</v>
@@ -1468,13 +1468,13 @@
         <v>1.8481</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1785</v>
+        <v>0.7147</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6856</v>
+        <v>0.1626</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4929</v>
+        <v>0.5522</v>
       </c>
       <c r="V13" t="n">
         <v>1.31</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4966</v>
+        <v>0.375</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3074</v>
+        <v>0.5657</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1892</v>
+        <v>-0.1908</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.8303</v>
+        <v>2.0962</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0383</v>
+        <v>-1.0929</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.792</v>
+        <v>3.1891</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1293</v>
+        <v>2.8005</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1557</v>
+        <v>-0.3173</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0264</v>
+        <v>3.1178</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9596</v>
+        <v>-0.7044</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.194</v>
+        <v>-0.7756</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7655999999999999</v>
+        <v>0.0713</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6427</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-3.2855</v>
       </c>
       <c r="R14" t="n">
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6842</v>
+        <v>-0.0785</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1781</v>
+        <v>-0.3682</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5061</v>
+        <v>0.2897</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.101</v>
+        <v>0.2037</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3565</v>
+        <v>-0.0064</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4576</v>
+        <v>0.2101</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0962</v>
+        <v>-1.8303</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0929</v>
+        <v>-1.0383</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1891</v>
+        <v>-0.792</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8005</v>
+        <v>0.1293</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3173</v>
+        <v>0.1557</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1178</v>
+        <v>-0.0264</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7044</v>
+        <v>-1.9596</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7756</v>
+        <v>-1.194</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0713</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.6427</v>
+        <v>1.6427</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2855</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5545</v>
+        <v>0.3913</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5774</v>
+        <v>-0.1357</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0229</v>
+        <v>0.527</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1599</v>
+        <v>-0.0348</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4899</v>
+        <v>-0.3427</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6498</v>
+        <v>0.308</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0146</v>
+        <v>0.4686</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.5821</v>
+        <v>-0.7234</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5967</v>
+        <v>1.192</v>
       </c>
       <c r="J16" t="n">
-        <v>2.106</v>
+        <v>0.0525</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.7222</v>
+        <v>-0.6974</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8282</v>
+        <v>0.7498</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0913</v>
+        <v>0.4161</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8599</v>
+        <v>-0.0261</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2314</v>
+        <v>0.4422</v>
       </c>
       <c r="P16" t="n">
         <v>0.2053</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0834</v>
+        <v>-0.5908</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1704</v>
+        <v>-0.3952</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2537</v>
+        <v>-0.1956</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2965</v>
+        <v>-0.1179</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5367</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2126</v>
+        <v>-0.186</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3427</v>
+        <v>1.1761</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1301</v>
+        <v>-1.3621</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4686</v>
+        <v>1.0146</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7234</v>
+        <v>-2.5821</v>
       </c>
       <c r="I17" t="n">
-        <v>1.192</v>
+        <v>3.5967</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0525</v>
+        <v>2.106</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6974</v>
+        <v>-1.7222</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7498</v>
+        <v>3.8282</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4161</v>
+        <v>-1.0913</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0261</v>
+        <v>-0.8599</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4422</v>
+        <v>-0.2314</v>
       </c>
       <c r="P17" t="n">
         <v>0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7687</v>
+        <v>-0.1095</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3952</v>
+        <v>-0.1434</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3734</v>
+        <v>0.034</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1179</v>
+        <v>-1.2965</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1179</v>
+        <v>-1.5367</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9528</v>
+        <v>-0.3077</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3156</v>
+        <v>0.5248</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2684</v>
+        <v>-0.8325</v>
       </c>
       <c r="G18" t="n">
         <v>2.4131</v>
@@ -1858,13 +1858,13 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2747</v>
+        <v>-0.6296</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2516</v>
+        <v>-1.0424</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0232</v>
+        <v>0.4127</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8858</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5685</v>
+        <v>-0.6916</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2475</v>
+        <v>0.3801</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.321</v>
+        <v>-1.0717</v>
       </c>
       <c r="G19" t="n">
         <v>1.5098</v>
@@ -1936,13 +1936,13 @@
         <v>2.2588</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1123</v>
+        <v>-0.2354</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1198</v>
+        <v>-0.4922</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0075</v>
+        <v>0.2568</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1179</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6965</v>
+        <v>-2.012</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1917</v>
+        <v>-0.7147</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5048</v>
+        <v>-1.2973</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4155</v>
@@ -2014,13 +2014,13 @@
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7271</v>
+        <v>0.4116</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8832</v>
+        <v>0.3602</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1561</v>
+        <v>0.0514</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4189</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6858</v>
+        <v>-2.5081</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1037</v>
+        <v>-2.7899</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4179</v>
+        <v>0.2819</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6423</v>
@@ -2092,13 +2092,13 @@
         <v>2.2588</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3076</v>
+        <v>-0.1298</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1857</v>
+        <v>-0.8719</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8781</v>
+        <v>0.7421</v>
       </c>
       <c r="V21" t="n">
         <v>-1.9947</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.8595</v>
+        <v>-5.5857</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.595</v>
+        <v>-4.4904</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2645</v>
+        <v>-1.0954</v>
       </c>
       <c r="G22" t="n">
         <v>-4.6851</v>
@@ -2170,13 +2170,13 @@
         <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1747</v>
+        <v>0.4484</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2517</v>
+        <v>0.3563</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.077</v>
+        <v>0.0921</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9384</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0053</v>
+        <v>-4.610700000000001</v>
       </c>
       <c r="E23" t="n">
         <v>-2.7332</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2723</v>
+        <v>-1.8775</v>
       </c>
       <c r="G23" t="n">
         <v>-2.893399999999999</v>
@@ -2248,13 +2248,13 @@
         <v>19.5074</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9107999999999999</v>
+        <v>0.4838999999999999</v>
       </c>
       <c r="T23" t="n">
         <v>-2.9072</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9965</v>
+        <v>3.3912</v>
       </c>
       <c r="V23" t="n">
         <v>-5.281499999999999</v>
